--- a/event_registration_forms/004_cardio_fitness_class_admission_form--event_registration_forms.xlsx
+++ b/event_registration_forms/004_cardio_fitness_class_admission_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -827,8 +827,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -856,12 +856,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'beginner_(new_to_cardio)',_'value':_'beginner'}</t>
+          <t>beginner_(new_to_cardio)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Beginner (New to cardio)', 'value': 'beginner'}</t>
+          <t>Beginner (New to cardio)</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'intermediate_(regularly_active)',_'value':_'intermediate'}</t>
+          <t>intermediate_(regularly_active)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Intermediate (Regularly active)', 'value': 'intermediate'}</t>
+          <t>Intermediate (Regularly active)</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'advanced_(high_fitness_level)',_'value':_'advanced'}</t>
+          <t>advanced_(high_fitness_level)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Advanced (High fitness level)', 'value': 'advanced'}</t>
+          <t>Advanced (High fitness level)</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree',_'value':_'agree'}</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'I Agree', 'value': 'agree'}</t>
+          <t>I Agree</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'i_disagree',_'value':_'disagree'}</t>
+          <t>i_disagree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'I Disagree', 'value': 'disagree'}</t>
+          <t>I Disagree</t>
         </is>
       </c>
     </row>
